--- a/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>GXAI</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,62 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -739,8 +746,14 @@
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -768,8 +781,14 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -797,8 +816,14 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,25 +835,27 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E12" s="3">
         <v>300</v>
       </c>
       <c r="F12" s="3">
+        <v>300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>300</v>
+      </c>
+      <c r="H12" s="3">
         <v>100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>200</v>
       </c>
       <c r="I12" s="3">
         <v>200</v>
@@ -836,11 +863,17 @@
       <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3">
+        <v>200</v>
+      </c>
+      <c r="L12" s="3">
+        <v>200</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,23 +901,29 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -897,8 +936,14 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -926,8 +971,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,37 +987,45 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E17" s="3">
         <v>800</v>
       </c>
       <c r="F17" s="3">
+        <v>900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>800</v>
+      </c>
+      <c r="H17" s="3">
         <v>1500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>300</v>
-      </c>
-      <c r="H17" s="3">
-        <v>300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>500</v>
       </c>
       <c r="J17" s="3">
         <v>300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="3">
+        <v>500</v>
+      </c>
+      <c r="L17" s="3">
+        <v>300</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -977,25 +1036,31 @@
         <v>-800</v>
       </c>
       <c r="F18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-500</v>
       </c>
       <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,8 +1072,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1033,11 +1100,17 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1048,25 +1121,31 @@
         <v>-800</v>
       </c>
       <c r="F21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1094,8 +1173,14 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1106,25 +1191,31 @@
         <v>-800</v>
       </c>
       <c r="F23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-500</v>
       </c>
       <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1152,8 +1243,14 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,8 +1278,14 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1193,25 +1296,31 @@
         <v>-800</v>
       </c>
       <c r="F26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-500</v>
       </c>
       <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1222,25 +1331,31 @@
         <v>-800</v>
       </c>
       <c r="F27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-500</v>
       </c>
       <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1383,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1418,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1453,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,8 +1488,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1381,11 +1520,17 @@
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1396,25 +1541,31 @@
         <v>-800</v>
       </c>
       <c r="F33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-500</v>
       </c>
       <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,8 +1593,14 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1454,59 +1611,71 @@
         <v>-800</v>
       </c>
       <c r="F35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-500</v>
       </c>
       <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1687,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,55 +1702,63 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F41" s="3">
         <v>800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F42" s="3">
         <v>3600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>3500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>3500</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1589,8 +1768,14 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1600,26 +1785,32 @@
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1647,22 +1838,28 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
       </c>
       <c r="H45" s="3">
         <v>200</v>
@@ -1671,42 +1868,54 @@
         <v>200</v>
       </c>
       <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="K45" s="3">
+        <v>200</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F46" s="3">
         <v>4400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1734,19 +1943,25 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1763,37 +1978,49 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>100</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>100</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +2048,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,8 +2083,14 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1879,8 +2118,14 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,37 +2153,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F54" s="3">
         <v>4400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1900</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2207,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,37 +2222,45 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
       </c>
       <c r="H57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>200</v>
       </c>
       <c r="J57" s="3">
+        <v>200</v>
+      </c>
+      <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2021,13 +2288,19 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>100</v>
@@ -2036,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H59" s="3">
         <v>0</v>
@@ -2047,40 +2320,52 @@
       <c r="J59" s="3">
         <v>0</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E60" s="3">
         <v>300</v>
       </c>
       <c r="F60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G60" s="3">
         <v>300</v>
       </c>
       <c r="H60" s="3">
+        <v>100</v>
+      </c>
+      <c r="I60" s="3">
+        <v>300</v>
+      </c>
+      <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>100</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2108,8 +2393,14 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2137,8 +2428,14 @@
       <c r="K62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2463,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2498,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,37 +2533,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E66" s="3">
         <v>300</v>
       </c>
       <c r="F66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G66" s="3">
         <v>300</v>
       </c>
       <c r="H66" s="3">
+        <v>100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>300</v>
+      </c>
+      <c r="J66" s="3">
         <v>200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2587,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2618,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2653,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2688,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,37 +2723,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-4600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-3700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-3000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2793,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2828,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,37 +2863,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F76" s="3">
         <v>4200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1800</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,42 +2933,54 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2602,25 +2991,31 @@
         <v>-800</v>
       </c>
       <c r="F81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-500</v>
       </c>
       <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,8 +3027,10 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2649,11 +3046,11 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -2661,8 +3058,14 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +3093,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +3128,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +3163,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +3198,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3233,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-900</v>
+        <v>-1100</v>
       </c>
       <c r="E89" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="F89" s="3">
         <v>-900</v>
       </c>
       <c r="G89" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="H89" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="I89" s="3">
         <v>-400</v>
       </c>
       <c r="J89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,13 +3287,15 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -2877,8 +3318,14 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3353,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,28 +3388,34 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-3500</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
@@ -2964,8 +3423,14 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,8 +3442,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3006,8 +3473,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3508,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3543,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,37 +3578,49 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>6000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3151,33 +3648,45 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3" t="s">
+      <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>GXAI</t>
   </si>
@@ -656,69 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -752,8 +756,11 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +794,11 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +832,11 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +850,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,7 +860,7 @@
         <v>200</v>
       </c>
       <c r="E12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F12" s="3">
         <v>300</v>
@@ -855,10 +869,10 @@
         <v>300</v>
       </c>
       <c r="H12" s="3">
+        <v>300</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>200</v>
       </c>
       <c r="J12" s="3">
         <v>200</v>
@@ -869,11 +883,14 @@
       <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3">
+        <v>200</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,26 +924,29 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -942,8 +962,11 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1000,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,43 +1015,47 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>300</v>
       </c>
       <c r="J17" s="3">
         <v>300</v>
       </c>
       <c r="K17" s="3">
+        <v>300</v>
+      </c>
+      <c r="L17" s="3">
         <v>500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1033,34 +1063,37 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-300</v>
       </c>
       <c r="J18" s="3">
         <v>-300</v>
       </c>
       <c r="K18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,8 +1107,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1083,7 +1117,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1106,11 +1140,14 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1118,23 +1155,23 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1144,8 +1181,11 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,43 +1219,49 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-300</v>
       </c>
       <c r="J23" s="3">
         <v>-300</v>
       </c>
       <c r="K23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L23" s="3">
         <v>-500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1295,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1333,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-300</v>
       </c>
       <c r="J26" s="3">
         <v>-300</v>
       </c>
       <c r="K26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-300</v>
       </c>
       <c r="J27" s="3">
         <v>-300</v>
       </c>
       <c r="K27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L27" s="3">
         <v>-500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1447,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1485,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,8 +1561,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1503,7 +1573,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1526,46 +1596,52 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-300</v>
       </c>
       <c r="J33" s="3">
         <v>-300</v>
       </c>
       <c r="K33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L33" s="3">
         <v>-500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1675,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-300</v>
       </c>
       <c r="J35" s="3">
         <v>-300</v>
       </c>
       <c r="K35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L35" s="3">
         <v>-500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,63 +1790,67 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E41" s="3">
         <v>3300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E42" s="3">
         <v>2100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3600</v>
-      </c>
-      <c r="G42" s="3">
-        <v>3500</v>
       </c>
       <c r="H42" s="3">
         <v>3500</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
+      <c r="I42" s="3">
+        <v>3500</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
@@ -1774,19 +1864,22 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+      <c r="F43" s="3">
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -1800,8 +1893,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1809,8 +1902,11 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1844,25 +1940,28 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>200</v>
@@ -1874,48 +1973,54 @@
         <v>200</v>
       </c>
       <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1900</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1949,8 +2054,11 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1961,10 +2069,10 @@
         <v>100</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1984,8 +2092,11 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1993,7 +2104,7 @@
         <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -2002,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <v>100</v>
@@ -2010,8 +2121,8 @@
       <c r="J49" s="3">
         <v>100</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>100</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2019,8 +2130,11 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,8 +2206,11 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2124,8 +2244,11 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2282,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E54" s="3">
         <v>6000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,16 +2354,17 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
-      </c>
-      <c r="E57" s="3">
-        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>200</v>
@@ -2242,10 +2373,10 @@
         <v>200</v>
       </c>
       <c r="H57" s="3">
+        <v>200</v>
+      </c>
+      <c r="I57" s="3">
         <v>100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>200</v>
@@ -2254,13 +2385,16 @@
         <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2294,8 +2428,11 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2306,14 +2443,14 @@
         <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
       <c r="I59" s="3">
         <v>0</v>
       </c>
@@ -2326,46 +2463,52 @@
       <c r="L59" s="3">
         <v>0</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>400</v>
+      </c>
+      <c r="E60" s="3">
         <v>500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>200</v>
       </c>
       <c r="K60" s="3">
         <v>200</v>
       </c>
       <c r="L60" s="3">
+        <v>200</v>
+      </c>
+      <c r="M60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2399,8 +2542,11 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2434,8 +2580,11 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2694,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>400</v>
+      </c>
+      <c r="E66" s="3">
         <v>500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>200</v>
       </c>
       <c r="K66" s="3">
         <v>200</v>
       </c>
       <c r="L66" s="3">
+        <v>200</v>
+      </c>
+      <c r="M66" s="3">
         <v>100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2900,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-5400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3052,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E76" s="3">
         <v>5500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1800</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3128,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-300</v>
       </c>
       <c r="J81" s="3">
         <v>-300</v>
       </c>
       <c r="K81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L81" s="3">
         <v>-500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,8 +3227,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3052,8 +3251,8 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3064,8 +3263,11 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3453,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,17 +3509,18 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -3324,8 +3545,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,31 +3621,34 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1000</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-3500</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3429,8 +3659,11 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3677,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3479,8 +3713,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,43 +3827,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>6000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3654,39 +3903,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E102" s="3">
         <v>2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3" t="s">
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>GXAI</t>
   </si>
@@ -656,81 +656,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -738,14 +742,14 @@
       <c r="G8" s="3">
         <v>0</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -759,8 +763,11 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -797,22 +804,25 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -835,8 +845,11 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,19 +864,20 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E12" s="3">
         <v>200</v>
       </c>
       <c r="F12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G12" s="3">
         <v>300</v>
@@ -872,10 +886,10 @@
         <v>300</v>
       </c>
       <c r="I12" s="3">
+        <v>300</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>200</v>
       </c>
       <c r="K12" s="3">
         <v>200</v>
@@ -886,11 +900,14 @@
       <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3">
+        <v>200</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,29 +944,32 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -965,8 +985,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1026,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,8 +1042,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1025,75 +1052,81 @@
         <v>900</v>
       </c>
       <c r="E17" s="3">
+        <v>900</v>
+      </c>
+      <c r="F17" s="3">
         <v>1000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>900</v>
       </c>
-      <c r="H17" s="3">
-        <v>800</v>
-      </c>
       <c r="I17" s="3">
+        <v>700</v>
+      </c>
+      <c r="J17" s="3">
         <v>1500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>300</v>
       </c>
       <c r="K17" s="3">
         <v>300</v>
       </c>
       <c r="L17" s="3">
+        <v>300</v>
+      </c>
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-900</v>
       </c>
       <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
-        <v>-800</v>
-      </c>
       <c r="I18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-300</v>
       </c>
       <c r="K18" s="3">
         <v>-300</v>
       </c>
       <c r="L18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,31 +1141,32 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1143,38 +1177,41 @@
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-900</v>
       </c>
       <c r="E21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
-        <v>-800</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-800</v>
-      </c>
       <c r="I21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1184,31 +1221,34 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1222,69 +1262,75 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-300</v>
       </c>
       <c r="K23" s="3">
         <v>-300</v>
       </c>
       <c r="L23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1298,8 +1344,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1385,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-300</v>
       </c>
       <c r="K26" s="3">
         <v>-300</v>
       </c>
       <c r="L26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-300</v>
       </c>
       <c r="K27" s="3">
         <v>-300</v>
       </c>
       <c r="L27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1508,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1549,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1590,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,31 +1631,34 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1599,49 +1669,55 @@
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-300</v>
       </c>
       <c r="K33" s="3">
         <v>-300</v>
       </c>
       <c r="L33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1754,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-300</v>
       </c>
       <c r="K35" s="3">
         <v>-300</v>
       </c>
       <c r="L35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1860,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,69 +1877,73 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E41" s="3">
         <v>2400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E42" s="3">
         <v>2300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3600</v>
-      </c>
-      <c r="H42" s="3">
-        <v>3500</v>
       </c>
       <c r="I42" s="3">
         <v>3500</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="J42" s="3">
+        <v>3500</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1867,22 +1957,25 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1896,8 +1989,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -1905,31 +1998,34 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1943,31 +2039,34 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
@@ -1976,74 +2075,80 @@
         <v>200</v>
       </c>
       <c r="M45" s="3">
+        <v>200</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1900</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2057,22 +2162,25 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>100</v>
-      </c>
-      <c r="E48" s="3">
-        <v>100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -2095,28 +2203,31 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>200</v>
+      </c>
+      <c r="F49" s="3">
+        <v>200</v>
+      </c>
+      <c r="G49" s="3">
         <v>100</v>
       </c>
-      <c r="E49" s="3">
-        <v>100</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>100</v>
@@ -2124,8 +2235,8 @@
       <c r="K49" s="3">
         <v>100</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>100</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2133,8 +2244,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2285,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,8 +2326,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2229,11 +2349,11 @@
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2247,8 +2367,11 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2408,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E54" s="3">
         <v>5100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2468,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,8 +2485,9 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2364,10 +2495,10 @@
         <v>300</v>
       </c>
       <c r="E57" s="3">
+        <v>300</v>
+      </c>
+      <c r="F57" s="3">
         <v>400</v>
-      </c>
-      <c r="F57" s="3">
-        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
@@ -2376,10 +2507,10 @@
         <v>200</v>
       </c>
       <c r="I57" s="3">
+        <v>200</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
@@ -2388,13 +2519,16 @@
         <v>200</v>
       </c>
       <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2431,31 +2565,34 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
-      </c>
-      <c r="E59" s="3">
-        <v>100</v>
-      </c>
-      <c r="F59" s="3">
-        <v>100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -2466,11 +2603,14 @@
       <c r="M59" s="3">
         <v>0</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2478,37 +2618,40 @@
         <v>400</v>
       </c>
       <c r="E60" s="3">
+        <v>400</v>
+      </c>
+      <c r="F60" s="3">
         <v>500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>300</v>
-      </c>
-      <c r="K60" s="3">
-        <v>200</v>
       </c>
       <c r="L60" s="3">
         <v>200</v>
       </c>
       <c r="M60" s="3">
+        <v>200</v>
+      </c>
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2545,31 +2688,34 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2583,8 +2729,11 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2770,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2811,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,8 +2852,11 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2706,37 +2864,40 @@
         <v>400</v>
       </c>
       <c r="E66" s="3">
+        <v>400</v>
+      </c>
+      <c r="F66" s="3">
         <v>500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>300</v>
-      </c>
-      <c r="K66" s="3">
-        <v>200</v>
       </c>
       <c r="L66" s="3">
         <v>200</v>
       </c>
       <c r="M66" s="3">
+        <v>200</v>
+      </c>
+      <c r="N66" s="3">
         <v>100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2912,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2951,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2992,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3033,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3074,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3156,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3197,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3238,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1800</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3320,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-300</v>
       </c>
       <c r="K81" s="3">
         <v>-300</v>
       </c>
       <c r="L81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,34 +3426,35 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3266,8 +3465,11 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3506,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3547,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3588,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3629,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,8 +3670,11 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3465,37 +3682,40 @@
         <v>-700</v>
       </c>
       <c r="E89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,31 +3730,32 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3548,8 +3769,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3810,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,34 +3851,37 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1000</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-3500</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
@@ -3662,8 +3892,11 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,31 +3911,32 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3716,8 +3950,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3991,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4032,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,69 +4073,75 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>6000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3906,42 +4155,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3" t="s">
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>GXAI</t>
   </si>
@@ -656,106 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
+      <c r="E8" s="3">
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -766,8 +773,14 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,28 +820,34 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+      <c r="E10" s="3">
+        <v>0</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -848,8 +867,14 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,37 +890,39 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
         <v>300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>300</v>
+      </c>
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>300</v>
       </c>
       <c r="I12" s="3">
         <v>300</v>
       </c>
       <c r="J12" s="3">
+        <v>300</v>
+      </c>
+      <c r="K12" s="3">
+        <v>300</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>200</v>
       </c>
       <c r="M12" s="3">
         <v>200</v>
@@ -903,11 +930,17 @@
       <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3">
+        <v>200</v>
+      </c>
+      <c r="P12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,35 +980,41 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -988,8 +1027,14 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1074,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,90 +1094,104 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="E17" s="3">
         <v>900</v>
       </c>
       <c r="F17" s="3">
+        <v>900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>900</v>
+      </c>
+      <c r="H17" s="3">
         <v>1000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>300</v>
-      </c>
-      <c r="M17" s="3">
-        <v>500</v>
       </c>
       <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3">
+        <v>500</v>
+      </c>
+      <c r="P17" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-900</v>
+        <v>-1400</v>
       </c>
       <c r="E18" s="3">
         <v>-900</v>
       </c>
       <c r="F18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-500</v>
       </c>
       <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,8 +1207,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1168,11 +1235,11 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1180,52 +1247,64 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-900</v>
       </c>
-      <c r="E21" s="3">
-        <v>-800</v>
-      </c>
       <c r="F21" s="3">
-        <v>-1000</v>
+        <v>-900</v>
       </c>
       <c r="G21" s="3">
         <v>-800</v>
       </c>
       <c r="H21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1250,11 +1329,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1265,13 +1344,19 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="E23" s="3">
         <v>-800</v>
@@ -1289,25 +1374,31 @@
         <v>-800</v>
       </c>
       <c r="J23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-500</v>
       </c>
       <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1332,11 +1423,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1347,8 +1438,14 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,13 +1485,19 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="E26" s="3">
         <v>-800</v>
@@ -1412,30 +1515,36 @@
         <v>-800</v>
       </c>
       <c r="J26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-500</v>
       </c>
       <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="E27" s="3">
         <v>-800</v>
@@ -1453,25 +1562,31 @@
         <v>-800</v>
       </c>
       <c r="J27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-500</v>
       </c>
       <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1626,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1673,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1720,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,8 +1767,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1660,11 +1799,11 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -1672,16 +1811,22 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="E33" s="3">
         <v>-800</v>
@@ -1699,25 +1844,31 @@
         <v>-800</v>
       </c>
       <c r="J33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L33" s="3">
         <v>-1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-500</v>
       </c>
       <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,13 +1908,19 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="E35" s="3">
         <v>-800</v>
@@ -1781,71 +1938,83 @@
         <v>-800</v>
       </c>
       <c r="J35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L35" s="3">
         <v>-1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-500</v>
       </c>
       <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2030,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,79 +2049,87 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F41" s="3">
         <v>5200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F42" s="3">
         <v>1600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>2300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>2100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>2600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>3600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>3500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>3500</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1960,28 +2139,34 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -1992,17 +2177,23 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2027,11 +2218,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2042,8 +2233,14 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2068,64 +2265,76 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
-        <v>200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>200</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M45" s="3">
         <v>200</v>
       </c>
       <c r="N45" s="3">
+        <v>200</v>
+      </c>
+      <c r="O45" s="3">
+        <v>200</v>
+      </c>
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F46" s="3">
         <v>6900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1900</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2150,11 +2359,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2165,13 +2374,19 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>100</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>3</v>
@@ -2206,13 +2421,19 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E49" s="3">
         <v>200</v>
@@ -2221,34 +2442,40 @@
         <v>200</v>
       </c>
       <c r="G49" s="3">
+        <v>200</v>
+      </c>
+      <c r="H49" s="3">
+        <v>200</v>
+      </c>
+      <c r="I49" s="3">
         <v>100</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>100</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>100</v>
+      </c>
+      <c r="N49" s="3">
+        <v>100</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2515,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,8 +2562,14 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2349,17 +2588,17 @@
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2370,8 +2609,14 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2656,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F54" s="3">
         <v>7100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1900</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2726,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,8 +2745,10 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2498,37 +2759,43 @@
         <v>300</v>
       </c>
       <c r="F57" s="3">
+        <v>300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>300</v>
+      </c>
+      <c r="H57" s="3">
         <v>400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>200</v>
       </c>
       <c r="I57" s="3">
         <v>200</v>
       </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
       <c r="L57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
       </c>
       <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
+        <v>200</v>
+      </c>
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2568,19 +2835,25 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
         <v>0</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2594,11 +2867,11 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -2606,52 +2879,64 @@
       <c r="N59" s="3">
         <v>0</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E60" s="3">
         <v>400</v>
       </c>
       <c r="F60" s="3">
+        <v>400</v>
+      </c>
+      <c r="G60" s="3">
+        <v>400</v>
+      </c>
+      <c r="H60" s="3">
         <v>500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>200</v>
       </c>
       <c r="I60" s="3">
         <v>300</v>
       </c>
       <c r="J60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K60" s="3">
         <v>300</v>
       </c>
       <c r="L60" s="3">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3">
+        <v>300</v>
+      </c>
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2691,8 +2976,14 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2717,11 +3008,11 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -2732,8 +3023,14 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3070,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3117,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3164,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E66" s="3">
         <v>400</v>
       </c>
       <c r="F66" s="3">
+        <v>400</v>
+      </c>
+      <c r="G66" s="3">
+        <v>400</v>
+      </c>
+      <c r="H66" s="3">
         <v>500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>300</v>
-      </c>
-      <c r="H66" s="3">
-        <v>200</v>
       </c>
       <c r="I66" s="3">
         <v>300</v>
       </c>
       <c r="J66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K66" s="3">
         <v>300</v>
       </c>
       <c r="L66" s="3">
+        <v>100</v>
+      </c>
+      <c r="M66" s="3">
+        <v>300</v>
+      </c>
+      <c r="N66" s="3">
         <v>200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3234,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3277,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3324,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3371,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3418,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-8000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-7100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-6300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-5400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-4600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-3700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-3000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3512,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3559,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3606,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F76" s="3">
         <v>6700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1800</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,59 +3700,71 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="E81" s="3">
         <v>-800</v>
@@ -3393,25 +3782,31 @@
         <v>-800</v>
       </c>
       <c r="J81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L81" s="3">
         <v>-1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-500</v>
       </c>
       <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,8 +3822,10 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3453,14 +3850,14 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3468,8 +3865,14 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3912,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3959,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4006,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4053,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +4100,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-700</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-1100</v>
       </c>
       <c r="G89" s="3">
         <v>-700</v>
       </c>
       <c r="H89" s="3">
-        <v>-900</v>
+        <v>-1100</v>
       </c>
       <c r="I89" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="J89" s="3">
         <v>-900</v>
       </c>
       <c r="K89" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="L89" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="M89" s="3">
         <v>-400</v>
       </c>
       <c r="N89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,8 +4170,10 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3757,11 +4198,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3772,8 +4213,14 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4260,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,40 +4307,46 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>1000</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-3500</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
@@ -3895,8 +4354,14 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,8 +4377,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3938,11 +4405,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3953,8 +4420,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4467,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4514,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,49 +4561,61 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F100" s="3">
         <v>2800</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>6000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4143,11 +4640,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4158,45 +4655,57 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F102" s="3">
         <v>2900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3" t="s">
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>GXAI</t>
   </si>
@@ -656,89 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>200</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -746,17 +750,17 @@
       <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+      <c r="J8" s="3">
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -764,8 +768,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -779,8 +783,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,13 +833,16 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -840,17 +850,17 @@
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -901,19 +915,19 @@
         <v>200</v>
       </c>
       <c r="E12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F12" s="3">
         <v>300</v>
       </c>
       <c r="G12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H12" s="3">
         <v>200</v>
       </c>
       <c r="I12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J12" s="3">
         <v>300</v>
@@ -922,10 +936,10 @@
         <v>300</v>
       </c>
       <c r="L12" s="3">
+        <v>300</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>200</v>
       </c>
       <c r="N12" s="3">
         <v>200</v>
@@ -936,11 +950,14 @@
       <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3">
+        <v>200</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1000,24 +1020,24 @@
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,16 +1122,17 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1400</v>
-      </c>
-      <c r="E17" s="3">
-        <v>900</v>
       </c>
       <c r="F17" s="3">
         <v>900</v>
@@ -1114,45 +1141,48 @@
         <v>900</v>
       </c>
       <c r="H17" s="3">
+        <v>900</v>
+      </c>
+      <c r="I17" s="3">
         <v>1000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1500</v>
-      </c>
-      <c r="M17" s="3">
-        <v>300</v>
       </c>
       <c r="N17" s="3">
         <v>300</v>
       </c>
       <c r="O17" s="3">
+        <v>300</v>
+      </c>
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-900</v>
       </c>
       <c r="F18" s="3">
         <v>-900</v>
@@ -1161,37 +1191,40 @@
         <v>-900</v>
       </c>
       <c r="H18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-300</v>
       </c>
       <c r="N18" s="3">
         <v>-300</v>
       </c>
       <c r="O18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1242,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1241,8 +1275,8 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1253,47 +1287,50 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-900</v>
       </c>
       <c r="F21" s="3">
         <v>-900</v>
       </c>
       <c r="G21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1303,8 +1340,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1335,8 +1375,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1350,55 +1390,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-300</v>
       </c>
       <c r="N23" s="3">
         <v>-300</v>
       </c>
       <c r="O23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1429,8 +1475,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-300</v>
       </c>
       <c r="N26" s="3">
         <v>-300</v>
       </c>
       <c r="O26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-300</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-300</v>
       </c>
       <c r="N27" s="3">
         <v>-300</v>
       </c>
       <c r="O27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1840,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1805,8 +1875,8 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -1817,58 +1887,64 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-300</v>
       </c>
       <c r="N33" s="3">
         <v>-300</v>
       </c>
       <c r="O33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-300</v>
       </c>
       <c r="N35" s="3">
         <v>-300</v>
       </c>
       <c r="O35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,87 +2137,91 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1800</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E42" s="3">
         <v>12300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3600</v>
-      </c>
-      <c r="K42" s="3">
-        <v>3500</v>
       </c>
       <c r="L42" s="3">
         <v>3500</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>3500</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -2145,16 +2235,19 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -2162,14 +2255,14 @@
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2183,8 +2276,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2192,8 +2285,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2224,8 +2320,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2239,8 +2335,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2271,8 +2370,8 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
-        <v>200</v>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
@@ -2281,60 +2380,66 @@
         <v>200</v>
       </c>
       <c r="P45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E46" s="3">
         <v>15200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1900</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2365,8 +2470,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2380,13 +2485,16 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>100</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>3</v>
@@ -2427,8 +2535,11 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2436,7 +2547,7 @@
         <v>900</v>
       </c>
       <c r="E49" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="F49" s="3">
         <v>200</v>
@@ -2448,16 +2559,16 @@
         <v>200</v>
       </c>
       <c r="I49" s="3">
+        <v>200</v>
+      </c>
+      <c r="J49" s="3">
         <v>100</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M49" s="3">
         <v>100</v>
@@ -2465,8 +2576,8 @@
       <c r="N49" s="3">
         <v>100</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>100</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2685,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2594,14 +2714,14 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E54" s="3">
         <v>16100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1900</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,8 +2877,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2765,10 +2896,10 @@
         <v>300</v>
       </c>
       <c r="H57" s="3">
+        <v>300</v>
+      </c>
+      <c r="I57" s="3">
         <v>400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>200</v>
@@ -2777,10 +2908,10 @@
         <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
         <v>100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>200</v>
       </c>
       <c r="N57" s="3">
         <v>200</v>
@@ -2789,13 +2920,16 @@
         <v>200</v>
       </c>
       <c r="P57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2841,8 +2975,11 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2855,8 +2992,8 @@
       <c r="F59" s="3">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+      <c r="G59" s="3">
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2873,8 +3010,8 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -2885,11 +3022,14 @@
       <c r="P59" s="3">
         <v>0</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2897,7 +3037,7 @@
         <v>500</v>
       </c>
       <c r="E60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F60" s="3">
         <v>400</v>
@@ -2906,37 +3046,40 @@
         <v>400</v>
       </c>
       <c r="H60" s="3">
+        <v>400</v>
+      </c>
+      <c r="I60" s="3">
         <v>500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
-      </c>
-      <c r="N60" s="3">
-        <v>200</v>
       </c>
       <c r="O60" s="3">
         <v>200</v>
       </c>
       <c r="P60" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2982,8 +3125,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3014,8 +3160,8 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,8 +3325,11 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3179,7 +3337,7 @@
         <v>500</v>
       </c>
       <c r="E66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F66" s="3">
         <v>400</v>
@@ -3188,37 +3346,40 @@
         <v>400</v>
       </c>
       <c r="H66" s="3">
+        <v>400</v>
+      </c>
+      <c r="I66" s="3">
         <v>500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>300</v>
-      </c>
-      <c r="N66" s="3">
-        <v>200</v>
       </c>
       <c r="O66" s="3">
         <v>200</v>
       </c>
       <c r="P66" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1800</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-300</v>
       </c>
       <c r="N81" s="3">
         <v>-300</v>
       </c>
       <c r="O81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4022,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3856,11 +4055,11 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -3871,8 +4070,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-800</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-700</v>
       </c>
       <c r="G89" s="3">
         <v>-700</v>
       </c>
       <c r="H89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4392,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4204,8 +4425,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -4219,8 +4440,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,43 +4540,46 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-3500</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4360,8 +4590,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4411,8 +4645,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,55 +4810,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>10700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2800</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>6000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4646,8 +4895,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4661,51 +4910,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3" t="s">
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>GXAI</t>
   </si>
@@ -656,121 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
+      <c r="L8" s="3">
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
@@ -778,8 +781,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -793,8 +796,11 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -846,37 +852,40 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
@@ -899,8 +908,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,25 +942,25 @@
         <v>300</v>
       </c>
       <c r="E12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
       </c>
       <c r="G12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H12" s="3">
         <v>300</v>
       </c>
       <c r="I12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J12" s="3">
         <v>200</v>
       </c>
       <c r="K12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L12" s="3">
         <v>300</v>
@@ -956,10 +969,10 @@
         <v>300</v>
       </c>
       <c r="N12" s="3">
+        <v>300</v>
+      </c>
+      <c r="O12" s="3">
         <v>100</v>
-      </c>
-      <c r="O12" s="3">
-        <v>200</v>
       </c>
       <c r="P12" s="3">
         <v>200</v>
@@ -970,11 +983,14 @@
       <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S12" s="3">
+        <v>200</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,8 +1042,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1046,24 +1065,24 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1079,13 +1098,16 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1132,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,22 +1175,23 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>900</v>
       </c>
       <c r="H17" s="3">
         <v>900</v>
@@ -1174,51 +1200,54 @@
         <v>900</v>
       </c>
       <c r="J17" s="3">
+        <v>900</v>
+      </c>
+      <c r="K17" s="3">
         <v>1000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
-      </c>
-      <c r="O17" s="3">
-        <v>300</v>
       </c>
       <c r="P17" s="3">
         <v>300</v>
       </c>
       <c r="Q17" s="3">
+        <v>300</v>
+      </c>
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-900</v>
       </c>
       <c r="H18" s="3">
         <v>-900</v>
@@ -1227,37 +1256,40 @@
         <v>-900</v>
       </c>
       <c r="J18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1500</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-300</v>
       </c>
       <c r="P18" s="3">
         <v>-300</v>
       </c>
       <c r="Q18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,8 +1309,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1315,8 +1348,8 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1327,53 +1360,56 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-900</v>
       </c>
       <c r="H21" s="3">
         <v>-900</v>
       </c>
       <c r="I21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1383,8 +1419,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1421,8 +1460,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1436,8 +1475,11 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1445,52 +1487,55 @@
         <v>-1100</v>
       </c>
       <c r="E23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1500</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-300</v>
       </c>
       <c r="P23" s="3">
         <v>-300</v>
       </c>
       <c r="Q23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1527,8 +1572,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1542,8 +1587,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,8 +1643,11 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1604,52 +1655,55 @@
         <v>-1100</v>
       </c>
       <c r="E26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1500</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-300</v>
       </c>
       <c r="P26" s="3">
         <v>-300</v>
       </c>
       <c r="Q26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R26" s="3">
         <v>-500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-300</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1657,52 +1711,55 @@
         <v>-1000</v>
       </c>
       <c r="E27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1500</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-300</v>
       </c>
       <c r="P27" s="3">
         <v>-300</v>
       </c>
       <c r="Q27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,8 +1979,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1951,8 +2020,8 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -1963,11 +2032,14 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1975,52 +2047,55 @@
         <v>-1000</v>
       </c>
       <c r="E33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1500</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-300</v>
       </c>
       <c r="P33" s="3">
         <v>-300</v>
       </c>
       <c r="Q33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,8 +2147,11 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2081,110 +2159,116 @@
         <v>-1000</v>
       </c>
       <c r="E35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1500</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-300</v>
       </c>
       <c r="P35" s="3">
         <v>-300</v>
       </c>
       <c r="Q35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,99 +2310,103 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>800</v>
+      </c>
+      <c r="E41" s="3">
         <v>900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1800</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E42" s="3">
         <v>12300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3600</v>
-      </c>
-      <c r="M42" s="3">
-        <v>3500</v>
       </c>
       <c r="N42" s="3">
         <v>3500</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3">
+        <v>3500</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
@@ -2331,8 +2420,11 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2340,13 +2432,13 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -2354,14 +2446,14 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
+      <c r="L43" s="3">
+        <v>0</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
@@ -2375,8 +2467,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2384,8 +2476,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2422,8 +2517,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2437,8 +2532,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2475,8 +2573,8 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
-        <v>200</v>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P45" s="3">
         <v>200</v>
@@ -2485,66 +2583,72 @@
         <v>200</v>
       </c>
       <c r="R45" s="3">
+        <v>200</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E46" s="3">
         <v>13400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1900</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2581,8 +2685,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2596,13 +2700,16 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>100</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>3</v>
@@ -2649,13 +2756,16 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="E49" s="3">
         <v>900</v>
@@ -2664,7 +2774,7 @@
         <v>900</v>
       </c>
       <c r="G49" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="H49" s="3">
         <v>200</v>
@@ -2676,16 +2786,16 @@
         <v>200</v>
       </c>
       <c r="K49" s="3">
+        <v>200</v>
+      </c>
+      <c r="L49" s="3">
         <v>100</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
       <c r="N49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O49" s="3">
         <v>100</v>
@@ -2693,8 +2803,8 @@
       <c r="P49" s="3">
         <v>100</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>100</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -2702,8 +2812,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,13 +2924,16 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2840,14 +2959,14 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -2861,8 +2980,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E54" s="3">
         <v>14300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1900</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,16 +3138,17 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>300</v>
       </c>
       <c r="F57" s="3">
         <v>300</v>
@@ -3033,10 +3163,10 @@
         <v>300</v>
       </c>
       <c r="J57" s="3">
+        <v>300</v>
+      </c>
+      <c r="K57" s="3">
         <v>400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
@@ -3045,10 +3175,10 @@
         <v>200</v>
       </c>
       <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
         <v>100</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
@@ -3057,13 +3187,16 @@
         <v>200</v>
       </c>
       <c r="R57" s="3">
+        <v>200</v>
+      </c>
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3115,13 +3248,16 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -3135,8 +3271,8 @@
       <c r="H59" s="3">
         <v>0</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
+      <c r="I59" s="3">
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -3153,8 +3289,8 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -3165,16 +3301,19 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E60" s="3">
         <v>500</v>
@@ -3183,7 +3322,7 @@
         <v>500</v>
       </c>
       <c r="G60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H60" s="3">
         <v>400</v>
@@ -3192,37 +3331,40 @@
         <v>400</v>
       </c>
       <c r="J60" s="3">
+        <v>400</v>
+      </c>
+      <c r="K60" s="3">
         <v>500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>300</v>
-      </c>
-      <c r="P60" s="3">
-        <v>200</v>
       </c>
       <c r="Q60" s="3">
         <v>200</v>
       </c>
       <c r="R60" s="3">
+        <v>200</v>
+      </c>
+      <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3274,8 +3416,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3312,8 +3457,8 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3327,8 +3472,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,13 +3640,16 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E66" s="3">
         <v>500</v>
@@ -3501,7 +3658,7 @@
         <v>500</v>
       </c>
       <c r="G66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H66" s="3">
         <v>400</v>
@@ -3510,37 +3667,40 @@
         <v>400</v>
       </c>
       <c r="J66" s="3">
+        <v>400</v>
+      </c>
+      <c r="K66" s="3">
         <v>500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>300</v>
-      </c>
-      <c r="P66" s="3">
-        <v>200</v>
       </c>
       <c r="Q66" s="3">
         <v>200</v>
       </c>
       <c r="R66" s="3">
+        <v>200</v>
+      </c>
+      <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3719,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E76" s="3">
         <v>14100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1800</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,66 +4278,72 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4157,52 +4351,55 @@
         <v>-1000</v>
       </c>
       <c r="E81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1500</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-300</v>
       </c>
       <c r="P81" s="3">
         <v>-300</v>
       </c>
       <c r="Q81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4260,11 +4458,11 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4275,8 +4473,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-700</v>
       </c>
       <c r="I89" s="3">
         <v>-700</v>
       </c>
       <c r="J89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4652,8 +4872,8 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -4667,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,49 +4999,52 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
         <v>300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1000</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-3500</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -4826,8 +5055,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4885,8 +5118,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4900,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,8 +5301,11 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5073,47 +5318,50 @@
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>10700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2800</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>3000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>6000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5150,8 +5398,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5165,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3" t="s">
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GXAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
   <si>
     <t>GXAI</t>
   </si>
@@ -656,127 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
+      <c r="M8" s="3">
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
@@ -784,8 +788,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -799,8 +803,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -855,40 +862,43 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
@@ -911,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,37 +946,38 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E12" s="3">
         <v>300</v>
       </c>
       <c r="F12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G12" s="3">
         <v>200</v>
       </c>
       <c r="H12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I12" s="3">
         <v>300</v>
       </c>
       <c r="J12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K12" s="3">
         <v>200</v>
       </c>
       <c r="L12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M12" s="3">
         <v>300</v>
@@ -972,10 +986,10 @@
         <v>300</v>
       </c>
       <c r="O12" s="3">
+        <v>300</v>
+      </c>
+      <c r="P12" s="3">
         <v>100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>200</v>
       </c>
       <c r="Q12" s="3">
         <v>200</v>
@@ -986,11 +1000,14 @@
       <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T12" s="3">
+        <v>200</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,13 +1062,16 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1068,24 +1088,24 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1101,8 +1121,11 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,25 +1202,26 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>900</v>
       </c>
       <c r="I17" s="3">
         <v>900</v>
@@ -1203,54 +1230,57 @@
         <v>900</v>
       </c>
       <c r="K17" s="3">
+        <v>900</v>
+      </c>
+      <c r="L17" s="3">
         <v>1000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1500</v>
-      </c>
-      <c r="P17" s="3">
-        <v>300</v>
       </c>
       <c r="Q17" s="3">
         <v>300</v>
       </c>
       <c r="R17" s="3">
+        <v>300</v>
+      </c>
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-900</v>
       </c>
       <c r="I18" s="3">
         <v>-900</v>
@@ -1259,37 +1289,40 @@
         <v>-900</v>
       </c>
       <c r="K18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-300</v>
       </c>
       <c r="Q18" s="3">
         <v>-300</v>
       </c>
       <c r="R18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,8 +1343,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1351,8 +1385,8 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1363,56 +1397,59 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1100</v>
+        <v>-2500</v>
       </c>
       <c r="E21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-900</v>
       </c>
       <c r="I21" s="3">
         <v>-900</v>
       </c>
       <c r="J21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1422,8 +1459,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1463,8 +1503,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1478,64 +1518,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1100</v>
+        <v>-2500</v>
       </c>
       <c r="E23" s="3">
         <v>-1100</v>
       </c>
       <c r="F23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-300</v>
       </c>
       <c r="Q23" s="3">
         <v>-300</v>
       </c>
       <c r="R23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1575,8 +1621,8 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1590,8 +1636,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1100</v>
+        <v>-2500</v>
       </c>
       <c r="E26" s="3">
         <v>-1100</v>
       </c>
       <c r="F26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-300</v>
       </c>
       <c r="Q26" s="3">
         <v>-300</v>
       </c>
       <c r="R26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S26" s="3">
         <v>-500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-300</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1000</v>
+        <v>-2200</v>
       </c>
       <c r="E27" s="3">
         <v>-1000</v>
       </c>
       <c r="F27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-300</v>
       </c>
       <c r="Q27" s="3">
         <v>-300</v>
       </c>
       <c r="R27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,8 +2049,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2023,8 +2093,8 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2035,67 +2105,73 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1000</v>
+        <v>-2200</v>
       </c>
       <c r="E33" s="3">
         <v>-1000</v>
       </c>
       <c r="F33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-300</v>
       </c>
       <c r="Q33" s="3">
         <v>-300</v>
       </c>
       <c r="R33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S33" s="3">
         <v>-500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1000</v>
+        <v>-2200</v>
       </c>
       <c r="E35" s="3">
         <v>-1000</v>
       </c>
       <c r="F35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-300</v>
       </c>
       <c r="Q35" s="3">
         <v>-300</v>
       </c>
       <c r="R35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S35" s="3">
         <v>-500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,105 +2397,109 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
         <v>800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1800</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E42" s="3">
         <v>11500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3600</v>
-      </c>
-      <c r="N42" s="3">
-        <v>3500</v>
       </c>
       <c r="O42" s="3">
         <v>3500</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3">
+        <v>3500</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
@@ -2423,8 +2513,11 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2435,13 +2528,13 @@
         <v>100</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="H43" s="3">
+        <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -2449,14 +2542,14 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3">
+        <v>0</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
@@ -2470,8 +2563,8 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2479,8 +2572,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2520,8 +2616,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2535,16 +2631,19 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+      <c r="E45" s="3">
+        <v>0</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -2576,8 +2675,8 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
-        <v>200</v>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
@@ -2586,74 +2685,80 @@
         <v>200</v>
       </c>
       <c r="S45" s="3">
+        <v>200</v>
+      </c>
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E46" s="3">
         <v>12600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1900</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>2900</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -2688,8 +2793,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2703,8 +2808,11 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2759,8 +2867,11 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2768,7 +2879,7 @@
         <v>700</v>
       </c>
       <c r="E49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F49" s="3">
         <v>900</v>
@@ -2777,7 +2888,7 @@
         <v>900</v>
       </c>
       <c r="H49" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="I49" s="3">
         <v>200</v>
@@ -2789,16 +2900,16 @@
         <v>200</v>
       </c>
       <c r="L49" s="3">
+        <v>200</v>
+      </c>
+      <c r="M49" s="3">
         <v>100</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
       <c r="O49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P49" s="3">
         <v>100</v>
@@ -2806,8 +2917,8 @@
       <c r="Q49" s="3">
         <v>100</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>100</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,16 +3044,19 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -2962,14 +3082,14 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E54" s="3">
         <v>13400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1900</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,19 +3269,20 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>300</v>
       </c>
       <c r="G57" s="3">
         <v>300</v>
@@ -3166,10 +3297,10 @@
         <v>300</v>
       </c>
       <c r="K57" s="3">
+        <v>300</v>
+      </c>
+      <c r="L57" s="3">
         <v>400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
@@ -3178,10 +3309,10 @@
         <v>200</v>
       </c>
       <c r="O57" s="3">
+        <v>200</v>
+      </c>
+      <c r="P57" s="3">
         <v>100</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
@@ -3190,13 +3321,16 @@
         <v>200</v>
       </c>
       <c r="S57" s="3">
+        <v>200</v>
+      </c>
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3251,17 +3385,20 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
       <c r="F59" s="3">
         <v>0</v>
       </c>
@@ -3274,8 +3411,8 @@
       <c r="I59" s="3">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -3292,8 +3429,8 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
@@ -3304,19 +3441,22 @@
       <c r="S59" s="3">
         <v>0</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>600</v>
+      </c>
+      <c r="E60" s="3">
         <v>700</v>
-      </c>
-      <c r="E60" s="3">
-        <v>500</v>
       </c>
       <c r="F60" s="3">
         <v>500</v>
@@ -3325,7 +3465,7 @@
         <v>500</v>
       </c>
       <c r="H60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I60" s="3">
         <v>400</v>
@@ -3334,37 +3474,40 @@
         <v>400</v>
       </c>
       <c r="K60" s="3">
+        <v>400</v>
+      </c>
+      <c r="L60" s="3">
         <v>500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>300</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>200</v>
       </c>
       <c r="R60" s="3">
         <v>200</v>
       </c>
       <c r="S60" s="3">
+        <v>200</v>
+      </c>
+      <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3419,8 +3562,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3460,8 +3606,8 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,16 +3798,19 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>600</v>
+      </c>
+      <c r="E66" s="3">
         <v>700</v>
-      </c>
-      <c r="E66" s="3">
-        <v>500</v>
       </c>
       <c r="F66" s="3">
         <v>500</v>
@@ -3661,7 +3819,7 @@
         <v>500</v>
       </c>
       <c r="H66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I66" s="3">
         <v>400</v>
@@ -3670,37 +3828,40 @@
         <v>400</v>
       </c>
       <c r="K66" s="3">
+        <v>400</v>
+      </c>
+      <c r="L66" s="3">
         <v>500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>300</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>200</v>
       </c>
       <c r="R66" s="3">
         <v>200</v>
       </c>
       <c r="S66" s="3">
+        <v>200</v>
+      </c>
+      <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E76" s="3">
         <v>13100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1800</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1000</v>
+        <v>-2200</v>
       </c>
       <c r="E81" s="3">
         <v>-1000</v>
       </c>
       <c r="F81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-300</v>
       </c>
       <c r="Q81" s="3">
         <v>-300</v>
       </c>
       <c r="R81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S81" s="3">
         <v>-500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4461,11 +4660,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-700</v>
       </c>
       <c r="J89" s="3">
         <v>-700</v>
       </c>
       <c r="K89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5054,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4875,8 +5096,8 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4890,8 +5111,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,52 +5229,55 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1000</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-3500</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5058,8 +5288,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5121,8 +5355,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,13 +5547,16 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>5300</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
@@ -5321,47 +5567,50 @@
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>10700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2800</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>3000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>6000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5401,8 +5650,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3" t="s">
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
